--- a/reports/Zabeel_Assets_Details_2026.xlsx
+++ b/reports/Zabeel_Assets_Details_2026.xlsx
@@ -12,7 +12,16 @@
     <sheet name="Zabeel Baby Room" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Zabeel Assets Summery" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Zabeel Washroom Details'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Zabeel Washroom Details'!$A$1:$J$17</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Zabeel Handicap Washroom'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Zabeel Handicap Washroom'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Zabeel Baby Room'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Zabeel Baby Room'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Zabeel Assets Summery'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Zabeel Assets Summery'!$A$1:$H$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -540,7 +549,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1101,6 +1110,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1108,7 +1118,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1449,6 +1459,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1456,7 +1467,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1624,6 +1635,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1631,7 +1643,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1762,5 +1774,6 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>